--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,14 +878,14 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>-50</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="N14" s="15">
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,37 +895,37 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="J15" s="14">
+        <v>3</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L15" s="15">
         <v>-50</v>
       </c>
-      <c r="I15" s="15">
-        <v>2</v>
-      </c>
-      <c r="J15" s="15">
-        <v>2</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>100</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>-33.333333333333</v>
       </c>
     </row>
@@ -933,164 +933,164 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>6</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
         <v>7</v>
       </c>
-      <c r="E16" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="F16" s="15">
-        <v>19</v>
-      </c>
-      <c r="G16" s="15">
-        <v>24</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-20.833333333333</v>
-      </c>
-      <c r="I16" s="15">
-        <v>28</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="D16" s="14">
+        <v>5</v>
+      </c>
+      <c r="E16" s="15">
+        <v>40</v>
+      </c>
+      <c r="F16" s="14">
+        <v>22</v>
+      </c>
+      <c r="G16" s="14">
+        <v>26</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-15.384615384615</v>
+      </c>
+      <c r="I16" s="14">
         <v>35</v>
       </c>
-      <c r="K16" s="14">
-        <v>-20</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-26.315789473684</v>
-      </c>
-      <c r="M16" s="14">
-        <v>47.368421052631</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-90.106007067137</v>
+      <c r="J16" s="14">
+        <v>40</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-14.634146341463</v>
+      </c>
+      <c r="M16" s="15">
+        <v>52.173913043478</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-88.993710691823</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>6</v>
-      </c>
-      <c r="D17" s="15">
-        <v>11</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-45.454545454545</v>
-      </c>
-      <c r="F17" s="15">
-        <v>31</v>
-      </c>
-      <c r="G17" s="15">
-        <v>36</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-13.888888888888</v>
-      </c>
-      <c r="I17" s="15">
-        <v>56</v>
-      </c>
-      <c r="J17" s="15">
-        <v>59</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-5.084745762711</v>
-      </c>
-      <c r="L17" s="14">
-        <v>14.285714285714</v>
-      </c>
-      <c r="M17" s="14">
-        <v>124</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-21.126760563380</v>
+      <c r="C17" s="14">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14">
+        <v>10</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>25</v>
+      </c>
+      <c r="G17" s="14">
+        <v>32</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-21.875</v>
+      </c>
+      <c r="I17" s="14">
+        <v>62</v>
+      </c>
+      <c r="J17" s="14">
+        <v>69</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-10.144927536231</v>
+      </c>
+      <c r="L17" s="15">
+        <v>1.639344262295</v>
+      </c>
+      <c r="M17" s="15">
+        <v>93.75</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-28.735632183908</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>50</v>
-      </c>
-      <c r="F18" s="15">
-        <v>18</v>
-      </c>
-      <c r="G18" s="15">
-        <v>31</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-41.935483870967</v>
-      </c>
-      <c r="I18" s="15">
-        <v>28</v>
-      </c>
-      <c r="J18" s="15">
-        <v>43</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-34.883720930232</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-39.130434782608</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-40.425531914893</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-91.411042944785</v>
+      <c r="D18" s="14">
+        <v>6</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>13</v>
+      </c>
+      <c r="G18" s="14">
+        <v>27</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-51.851851851851</v>
+      </c>
+      <c r="I18" s="14">
+        <v>32</v>
+      </c>
+      <c r="J18" s="14">
+        <v>49</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-34.693877551020</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-34.693877551020</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-91.351351351351</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>23</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="14">
         <v>40</v>
       </c>
-      <c r="E19" s="14">
-        <v>-42.5</v>
-      </c>
-      <c r="F19" s="15">
-        <v>103</v>
-      </c>
-      <c r="G19" s="15">
-        <v>130</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-20.769230769230</v>
-      </c>
-      <c r="I19" s="15">
-        <v>171</v>
-      </c>
-      <c r="J19" s="15">
-        <v>213</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-19.718309859154</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-45.192307692307</v>
-      </c>
-      <c r="M19" s="14">
-        <v>-33.203125</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-85.194805194805</v>
+      <c r="D19" s="14">
+        <v>38</v>
+      </c>
+      <c r="E19" s="15">
+        <v>5.263157894736</v>
+      </c>
+      <c r="F19" s="14">
+        <v>116</v>
+      </c>
+      <c r="G19" s="14">
+        <v>133</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-12.781954887218</v>
+      </c>
+      <c r="I19" s="14">
+        <v>209</v>
+      </c>
+      <c r="J19" s="14">
+        <v>251</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-16.733067729083</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-39.942528735632</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-28.911564625850</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-84.057971014492</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1109,28 +1109,28 @@
       <c r="F20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <v>2</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
         <v>-100</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="14">
         <v>2</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="15">
         <v>-100</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="15">
         <v>-100</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="15">
         <v>-100</v>
       </c>
-      <c r="N20" s="14">
+      <c r="N20" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D21" s="17">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E21" s="18">
-        <v>-38.709677419354</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G21" s="17">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.555555555555</v>
+        <v>-20.179372197309</v>
       </c>
       <c r="I21" s="17">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="J21" s="17">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.491525423728</v>
+        <v>-17.632850241545</v>
       </c>
       <c r="L21" s="18">
-        <v>-37.224669603524</v>
+        <v>-33.137254901960</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.803418803418</v>
+        <v>-17.031630170316</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.928609201480</v>
+        <v>-84.146908414690</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
-      </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
-        <v>11</v>
-      </c>
-      <c r="G22" s="15">
-        <v>16</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-31.25</v>
-      </c>
-      <c r="I22" s="15">
-        <v>17</v>
-      </c>
-      <c r="J22" s="15">
-        <v>19</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-10.526315789473</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-32</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-19.047619047619</v>
+      <c r="C22" s="14">
+        <v>5</v>
+      </c>
+      <c r="D22" s="14">
+        <v>6</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="F22" s="14">
+        <v>14</v>
+      </c>
+      <c r="G22" s="14">
+        <v>15</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-6.666666666666</v>
+      </c>
+      <c r="I22" s="14">
+        <v>23</v>
+      </c>
+      <c r="J22" s="14">
+        <v>25</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-8</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-20.689655172413</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-4.166666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>69</v>
-      </c>
-      <c r="D24" s="15">
-        <v>80</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-13.75</v>
-      </c>
-      <c r="F24" s="15">
-        <v>301</v>
-      </c>
-      <c r="G24" s="15">
-        <v>301</v>
-      </c>
-      <c r="H24" s="14">
+      <c r="C24" s="14">
+        <v>83</v>
+      </c>
+      <c r="D24" s="14">
+        <v>72</v>
+      </c>
+      <c r="E24" s="15">
+        <v>15.277777777777</v>
+      </c>
+      <c r="F24" s="14">
+        <v>302</v>
+      </c>
+      <c r="G24" s="14">
+        <v>302</v>
+      </c>
+      <c r="H24" s="15">
         <v>0</v>
       </c>
-      <c r="I24" s="15">
-        <v>403</v>
-      </c>
-      <c r="J24" s="15">
-        <v>414</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-2.657004830917</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-5.841121495327</v>
-      </c>
-      <c r="M24" s="14">
-        <v>-16.216216216216</v>
+      <c r="I24" s="14">
+        <v>485</v>
+      </c>
+      <c r="J24" s="14">
+        <v>486</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-0.205761316872</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-7.619047619047</v>
+      </c>
+      <c r="M24" s="15">
+        <v>-14.159292035398</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>62</v>
-      </c>
-      <c r="D25" s="15">
-        <v>83</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-25.301204819277</v>
-      </c>
-      <c r="F25" s="15">
+      <c r="C25" s="14">
+        <v>68</v>
+      </c>
+      <c r="D25" s="14">
+        <v>56</v>
+      </c>
+      <c r="E25" s="15">
+        <v>21.428571428571</v>
+      </c>
+      <c r="F25" s="14">
         <v>258</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="14">
         <v>275</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="15">
         <v>-6.181818181818</v>
       </c>
-      <c r="I25" s="15">
-        <v>345</v>
-      </c>
-      <c r="J25" s="15">
-        <v>375</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-8</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-2.816901408450</v>
+      <c r="I25" s="14">
+        <v>412</v>
+      </c>
+      <c r="J25" s="14">
+        <v>431</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-4.408352668213</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-4.629629629629</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>27</v>
-      </c>
-      <c r="D26" s="15">
-        <v>20</v>
-      </c>
-      <c r="E26" s="14">
-        <v>35</v>
-      </c>
-      <c r="F26" s="15">
-        <v>91</v>
-      </c>
-      <c r="G26" s="15">
-        <v>81</v>
-      </c>
-      <c r="H26" s="14">
-        <v>12.345679012345</v>
-      </c>
-      <c r="I26" s="15">
-        <v>118</v>
-      </c>
-      <c r="J26" s="15">
-        <v>118</v>
-      </c>
-      <c r="K26" s="14">
-        <v>0</v>
-      </c>
-      <c r="L26" s="14">
-        <v>10.280373831775</v>
-      </c>
-      <c r="M26" s="14">
-        <v>103.448275862069</v>
+      <c r="C26" s="14">
+        <v>29</v>
+      </c>
+      <c r="D26" s="14">
+        <v>12</v>
+      </c>
+      <c r="E26" s="15">
+        <v>141.666666666667</v>
+      </c>
+      <c r="F26" s="14">
+        <v>95</v>
+      </c>
+      <c r="G26" s="14">
+        <v>69</v>
+      </c>
+      <c r="H26" s="15">
+        <v>37.681159420289</v>
+      </c>
+      <c r="I26" s="14">
+        <v>147</v>
+      </c>
+      <c r="J26" s="14">
+        <v>130</v>
+      </c>
+      <c r="K26" s="15">
+        <v>13.076923076923</v>
+      </c>
+      <c r="L26" s="15">
+        <v>13.953488372093</v>
+      </c>
+      <c r="M26" s="15">
+        <v>104.166666666667</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
-        <v>3</v>
-      </c>
-      <c r="H27" s="14">
+      <c r="J27" s="14">
+        <v>4</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L27" s="15">
         <v>-66.666666666666</v>
-      </c>
-      <c r="I27" s="15">
-        <v>2</v>
-      </c>
-      <c r="J27" s="15">
-        <v>3</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L27" s="14">
-        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>5</v>
-      </c>
-      <c r="D28" s="15">
-        <v>4</v>
-      </c>
-      <c r="E28" s="14">
-        <v>25</v>
-      </c>
-      <c r="F28" s="15">
-        <v>16</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>200</v>
+      </c>
+      <c r="F28" s="14">
         <v>15</v>
       </c>
-      <c r="H28" s="14">
-        <v>6.666666666666</v>
-      </c>
-      <c r="I28" s="15">
-        <v>22</v>
-      </c>
-      <c r="J28" s="15">
-        <v>19</v>
-      </c>
-      <c r="K28" s="14">
-        <v>15.789473684210</v>
-      </c>
-      <c r="L28" s="14">
-        <v>15.789473684210</v>
+      <c r="G28" s="14">
+        <v>10</v>
+      </c>
+      <c r="H28" s="15">
+        <v>50</v>
+      </c>
+      <c r="I28" s="14">
+        <v>24</v>
+      </c>
+      <c r="J28" s="14">
+        <v>20</v>
+      </c>
+      <c r="K28" s="15">
+        <v>20</v>
+      </c>
+      <c r="L28" s="15">
+        <v>26.315789473684</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1493,22 +1493,22 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="14">
-        <v>-100</v>
+      <c r="L29" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="15">
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1534,46 +1534,46 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="14">
-        <v>-100</v>
+      <c r="L30" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="15">
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>4</v>
+      </c>
+      <c r="G31" s="14">
         <v>2</v>
       </c>
-      <c r="H31" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I31" s="15">
-        <v>1</v>
-      </c>
-      <c r="J31" s="15">
-        <v>3</v>
-      </c>
-      <c r="K31" s="14">
-        <v>-66.666666666666</v>
+      <c r="H31" s="15">
+        <v>100</v>
+      </c>
+      <c r="I31" s="14">
+        <v>5</v>
+      </c>
+      <c r="J31" s="14">
+        <v>4</v>
+      </c>
+      <c r="K31" s="15">
+        <v>25</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>8</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>11</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>3</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>4</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>2</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-50</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-81.818181818181</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-75</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>41</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>41</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>15</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>12</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>32</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>166.666666666667</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>113.333333333333</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-21.951219512195</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-21.951219512195</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>4227</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>2520</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>881</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>528</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>353</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-33.143939393939</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-59.931895573212</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-85.992063492063</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-91.648923586467</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>1116</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>670</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>397</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>318</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>548</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>72.327044025157</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>38.035264483627</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-18.208955223880</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-50.896057347670</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>3513</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>2687</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>1020</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>876</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>430</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-50.913242009132</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-57.843137254902</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-83.997022701898</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-87.759749501850</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>13326</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>9365</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>5133</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>4245</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>1759</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-58.563015312131</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-65.731541009156</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-81.217298451681</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-86.800240132072</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>612</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>356</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>188</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>103</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>23</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-77.669902912621</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-87.765957446808</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-93.539325842696</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-96.241830065359</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>-15.384615384615</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.5</v>
+        <v>-6.25</v>
       </c>
       <c r="L16" s="15">
-        <v>-14.634146341463</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="M16" s="15">
-        <v>52.173913043478</v>
+        <v>60.714285714285</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.993710691823</v>
+        <v>-87.394957983193</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.875</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="J17" s="14">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.144927536231</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="L17" s="15">
-        <v>1.639344262295</v>
+        <v>-6.410256410256</v>
       </c>
       <c r="M17" s="15">
-        <v>93.75</v>
+        <v>102.777777777778</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.735632183908</v>
+        <v>-24.742268041237</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H18" s="15">
-        <v>-51.851851851851</v>
+        <v>-71.875</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.693877551020</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="L18" s="15">
-        <v>-34.693877551020</v>
+        <v>-42.372881355932</v>
       </c>
       <c r="M18" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.262295081967</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.351351351351</v>
+        <v>-91.962174940898</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D19" s="14">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E19" s="15">
-        <v>5.263157894736</v>
+        <v>17.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G19" s="14">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.781954887218</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="I19" s="14">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="J19" s="14">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.733067729083</v>
+        <v>-13.261648745519</v>
       </c>
       <c r="L19" s="15">
-        <v>-39.942528735632</v>
+        <v>-36.315789473684</v>
       </c>
       <c r="M19" s="15">
-        <v>-28.911564625850</v>
+        <v>-27.761194029850</v>
       </c>
       <c r="N19" s="15">
-        <v>-84.057971014492</v>
+        <v>-83.823529411764</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
@@ -1119,7 +1119,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="15">
         <v>-100</v>
@@ -1142,37 +1142,37 @@
         <v>56</v>
       </c>
       <c r="D21" s="17">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.666666666666</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="F21" s="17">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G21" s="17">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.179372197309</v>
+        <v>-17.748917748917</v>
       </c>
       <c r="I21" s="17">
-        <v>341</v>
+        <v>399</v>
       </c>
       <c r="J21" s="17">
-        <v>414</v>
+        <v>476</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.632850241545</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="L21" s="18">
-        <v>-33.137254901960</v>
+        <v>-30.849220103986</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.031630170316</v>
+        <v>-14.377682403433</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.146908414690</v>
+        <v>-83.647540983606</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>-16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
+        <v>17</v>
+      </c>
+      <c r="G22" s="14">
         <v>14</v>
       </c>
-      <c r="G22" s="14">
-        <v>15</v>
-      </c>
       <c r="H22" s="15">
-        <v>-6.666666666666</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I22" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J22" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K22" s="15">
-        <v>-8</v>
+        <v>3.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>-20.689655172413</v>
+        <v>-9.375</v>
       </c>
       <c r="M22" s="15">
-        <v>-4.166666666666</v>
+        <v>7.407407407407</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D24" s="14">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E24" s="15">
-        <v>15.277777777777</v>
+        <v>-20.238095238095</v>
       </c>
       <c r="F24" s="14">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="G24" s="14">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-8.038585209003</v>
       </c>
       <c r="I24" s="14">
-        <v>485</v>
+        <v>552</v>
       </c>
       <c r="J24" s="14">
-        <v>486</v>
+        <v>570</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.205761316872</v>
+        <v>-3.157894736842</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.619047619047</v>
+        <v>-8</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.159292035398</v>
+        <v>-15.337423312883</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D25" s="14">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="E25" s="15">
-        <v>21.428571428571</v>
+        <v>-32.911392405063</v>
       </c>
       <c r="F25" s="14">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="G25" s="14">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H25" s="15">
-        <v>-6.181818181818</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>412</v>
+        <v>467</v>
       </c>
       <c r="J25" s="14">
-        <v>431</v>
+        <v>510</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.408352668213</v>
+        <v>-8.431372549019</v>
       </c>
       <c r="L25" s="15">
-        <v>-4.629629629629</v>
+        <v>-5.656565656565</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>141.666666666667</v>
+        <v>73.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G26" s="14">
         <v>69</v>
       </c>
       <c r="H26" s="15">
-        <v>37.681159420289</v>
+        <v>46.376811594202</v>
       </c>
       <c r="I26" s="14">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="J26" s="14">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="K26" s="15">
-        <v>13.076923076923</v>
+        <v>18.620689655172</v>
       </c>
       <c r="L26" s="15">
-        <v>13.953488372093</v>
+        <v>14.666666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>104.166666666667</v>
+        <v>102.352941176471</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="I27" s="14">
         <v>4</v>
       </c>
-      <c r="H27" s="15">
-        <v>-75</v>
-      </c>
-      <c r="I27" s="14">
-        <v>2</v>
-      </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
         <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-62.5</v>
       </c>
       <c r="F28" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>26.315789473684</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1548,14 +1548,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H15" s="15">
-        <v>-57.142857142857</v>
+        <v>-80</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-42.857142857142</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="15">
         <v>-20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>12.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
+        <v>25</v>
+      </c>
+      <c r="G16" s="14">
         <v>26</v>
       </c>
-      <c r="G16" s="14">
-        <v>23</v>
-      </c>
       <c r="H16" s="15">
-        <v>13.043478260869</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I16" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J16" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.25</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="L16" s="15">
-        <v>-4.255319148936</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="M16" s="15">
-        <v>60.714285714285</v>
+        <v>51.612903225806</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.394957983193</v>
+        <v>-88.220551378446</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>-20</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="I17" s="14">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="J17" s="14">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.194805194805</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.410256410256</v>
+        <v>-10</v>
       </c>
       <c r="M17" s="15">
-        <v>102.777777777778</v>
+        <v>113.157894736842</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.742268041237</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-84.615384615384</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18" s="15">
-        <v>-71.875</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.161290322580</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.372881355932</v>
+        <v>-34.375</v>
       </c>
       <c r="M18" s="15">
-        <v>-44.262295081967</v>
+        <v>-37.313432835820</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.962174940898</v>
+        <v>-91.139240506329</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D19" s="14">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E19" s="15">
-        <v>17.857142857142</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F19" s="14">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G19" s="14">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.818181818181</v>
+        <v>-15.277777777777</v>
       </c>
       <c r="I19" s="14">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="J19" s="14">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.261648745519</v>
+        <v>-15.457413249211</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.315789473684</v>
+        <v>-34.152334152334</v>
       </c>
       <c r="M19" s="15">
-        <v>-27.761194029850</v>
+        <v>-27.371273712737</v>
       </c>
       <c r="N19" s="15">
-        <v>-83.823529411764</v>
+        <v>-83.826191913096</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+        <v>200</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="I20" s="14">
+        <v>3</v>
       </c>
       <c r="J20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
-        <v>-100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M20" s="15">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-100</v>
+        <v>-95.714285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.677419354838</v>
+        <v>-35.820895522388</v>
       </c>
       <c r="F21" s="17">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G21" s="17">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.748917748917</v>
+        <v>-21.115537848605</v>
       </c>
       <c r="I21" s="17">
-        <v>399</v>
+        <v>446</v>
       </c>
       <c r="J21" s="17">
-        <v>476</v>
+        <v>543</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.176470588235</v>
+        <v>-17.863720073664</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.849220103986</v>
+        <v>-28.867623604465</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.377682403433</v>
+        <v>-12.720156555773</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.647540983606</v>
+        <v>-83.560633984519</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>6</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G22" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="15">
-        <v>21.428571428571</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>29</v>
       </c>
       <c r="J22" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K22" s="15">
-        <v>3.571428571428</v>
+        <v>-9.375</v>
       </c>
       <c r="L22" s="15">
         <v>-9.375</v>
       </c>
       <c r="M22" s="15">
-        <v>7.407407407407</v>
+        <v>3.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D24" s="14">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.238095238095</v>
+        <v>-33.783783783783</v>
       </c>
       <c r="F24" s="14">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="G24" s="14">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.038585209003</v>
+        <v>-13.548387096774</v>
       </c>
       <c r="I24" s="14">
-        <v>552</v>
+        <v>601</v>
       </c>
       <c r="J24" s="14">
-        <v>570</v>
+        <v>644</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.157894736842</v>
+        <v>-6.677018633540</v>
       </c>
       <c r="L24" s="15">
-        <v>-8</v>
+        <v>-12.518195050946</v>
       </c>
       <c r="M24" s="15">
-        <v>-15.337423312883</v>
+        <v>-18.119891008174</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D25" s="14">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="E25" s="15">
-        <v>-32.911392405063</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="G25" s="14">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.857142857142</v>
+        <v>-20.143884892086</v>
       </c>
       <c r="I25" s="14">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="J25" s="14">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.431372549019</v>
+        <v>-11.578947368421</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.656565656565</v>
+        <v>-11.733800350262</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>73.333333333333</v>
+        <v>10</v>
       </c>
       <c r="F26" s="14">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G26" s="14">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H26" s="15">
-        <v>46.376811594202</v>
+        <v>53.731343283582</v>
       </c>
       <c r="I26" s="14">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="J26" s="14">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="K26" s="15">
-        <v>18.620689655172</v>
+        <v>16.969696969697</v>
       </c>
       <c r="L26" s="15">
-        <v>14.666666666666</v>
+        <v>16.969696969697</v>
       </c>
       <c r="M26" s="15">
-        <v>102.352941176471</v>
+        <v>103.157894736842</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>4</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H27" s="15">
-        <v>-57.142857142857</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L27" s="15">
         <v>-42.857142857142</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>-62.5</v>
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="15">
-        <v>-23.529411764705</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.571428571428</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="L28" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1561,19 +1561,19 @@
         <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -905,19 +905,19 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H15" s="15">
-        <v>-80</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L15" s="15">
         <v>-20</v>
@@ -926,7 +926,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-3.846153846153</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J16" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.962962962963</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="L16" s="15">
-        <v>-9.615384615384</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="M16" s="15">
-        <v>51.612903225806</v>
+        <v>51.515151515151</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.220551378446</v>
+        <v>-88.636363636363</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.684210526315</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.813953488372</v>
+        <v>-3.191489361702</v>
       </c>
       <c r="L17" s="15">
-        <v>-10</v>
+        <v>-14.953271028037</v>
       </c>
       <c r="M17" s="15">
-        <v>113.157894736842</v>
+        <v>121.951219512195</v>
       </c>
       <c r="N17" s="15">
-        <v>-25</v>
+        <v>-24.166666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>-92.307692307692</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H18" s="15">
-        <v>-48.387096774193</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.666666666666</v>
+        <v>-49.411764705882</v>
       </c>
       <c r="L18" s="15">
-        <v>-34.375</v>
+        <v>-41.891891891891</v>
       </c>
       <c r="M18" s="15">
-        <v>-37.313432835820</v>
+        <v>-40.277777777777</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.139240506329</v>
+        <v>-91.917293233082</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D19" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E19" s="15">
-        <v>-31.578947368421</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G19" s="14">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.277777777777</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="I19" s="14">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="J19" s="14">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.457413249211</v>
+        <v>-12.607449856733</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.152334152334</v>
+        <v>-31.767337807606</v>
       </c>
       <c r="M19" s="15">
-        <v>-27.371273712737</v>
+        <v>-25.427872860635</v>
       </c>
       <c r="N19" s="15">
-        <v>-83.826191913096</v>
+        <v>-83.204845814978</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>200</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-57.142857142857</v>
+        <v>-75</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.714285714285</v>
+        <v>-97.368421052631</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E21" s="18">
-        <v>-35.820895522388</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="F21" s="17">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G21" s="17">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.115537848605</v>
+        <v>-15.447154471544</v>
       </c>
       <c r="I21" s="17">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="J21" s="17">
-        <v>543</v>
+        <v>600</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.863720073664</v>
+        <v>-17.333333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.867623604465</v>
+        <v>-29.243937232525</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.720156555773</v>
+        <v>-11.743772241992</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.560633984519</v>
+        <v>-83.422459893048</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
         <v>13</v>
       </c>
       <c r="G22" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="15">
-        <v>-13.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="I22" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J22" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K22" s="15">
-        <v>-9.375</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="L22" s="15">
-        <v>-9.375</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M22" s="15">
-        <v>3.571428571428</v>
+        <v>10.714285714285</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D24" s="14">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.783783783783</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="G24" s="14">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.548387096774</v>
+        <v>-13.907284768211</v>
       </c>
       <c r="I24" s="14">
-        <v>601</v>
+        <v>660</v>
       </c>
       <c r="J24" s="14">
-        <v>644</v>
+        <v>716</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.677018633540</v>
+        <v>-7.821229050279</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.518195050946</v>
+        <v>-14.618369987063</v>
       </c>
       <c r="M24" s="15">
-        <v>-18.119891008174</v>
+        <v>-18.316831683168</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D25" s="14">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.666666666666</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F25" s="14">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G25" s="14">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.143884892086</v>
+        <v>-15.079365079365</v>
       </c>
       <c r="I25" s="14">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="J25" s="14">
-        <v>570</v>
+        <v>627</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.578947368421</v>
+        <v>-11.004784688995</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.733800350262</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
         <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>10</v>
+        <v>-35</v>
       </c>
       <c r="F26" s="14">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G26" s="14">
         <v>67</v>
       </c>
       <c r="H26" s="15">
-        <v>53.731343283582</v>
+        <v>32.835820895522</v>
       </c>
       <c r="I26" s="14">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="J26" s="14">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="K26" s="15">
-        <v>16.969696969697</v>
+        <v>11.351351351351</v>
       </c>
       <c r="L26" s="15">
-        <v>16.969696969697</v>
+        <v>10.752688172043</v>
       </c>
       <c r="M26" s="15">
-        <v>103.157894736842</v>
+        <v>83.928571428571</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
@@ -1397,19 +1397,19 @@
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>-80</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-63.636363636363</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="15">
         <v>-42.857142857142</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>25</v>
       </c>
       <c r="F28" s="14">
         <v>12</v>
@@ -1444,16 +1444,16 @@
         <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J28" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.151515151515</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,7 +1494,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
         <v>0</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>50</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="L31" s="15">
+        <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -914,13 +914,13 @@
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-63.636363636363</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
         <v>300</v>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.280701754386</v>
+        <v>-17.1875</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.793103448275</v>
+        <v>-17.1875</v>
       </c>
       <c r="M16" s="15">
-        <v>51.515151515151</v>
+        <v>43.243243243243</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.636363636363</v>
+        <v>-89.117043121149</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.714285714285</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J17" s="14">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.191489361702</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.953271028037</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="M17" s="15">
-        <v>121.951219512195</v>
+        <v>113.04347826087</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.166666666666</v>
+        <v>-27.941176470588</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E18" s="15">
-        <v>-92.307692307692</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.153846153846</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J18" s="14">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.411764705882</v>
+        <v>-53.465346534653</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.891891891891</v>
+        <v>-45.348837209302</v>
       </c>
       <c r="M18" s="15">
-        <v>-40.277777777777</v>
+        <v>-38.961038961039</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.917293233082</v>
+        <v>-91.754385964912</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>36</v>
       </c>
       <c r="D19" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>24.137931034482</v>
       </c>
       <c r="F19" s="14">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G19" s="14">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.470588235294</v>
+        <v>3.149606299212</v>
       </c>
       <c r="I19" s="14">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="J19" s="14">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.607449856733</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.767337807606</v>
+        <v>-28.301886792452</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.427872860635</v>
+        <v>-23.660714285714</v>
       </c>
       <c r="N19" s="15">
-        <v>-83.204845814978</v>
+        <v>-82.586558044806</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M20" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.368421052631</v>
+        <v>-97.468354430379</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.280701754386</v>
+        <v>-24.615384615384</v>
       </c>
       <c r="F21" s="17">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G21" s="17">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.447154471544</v>
+        <v>-19.521912350597</v>
       </c>
       <c r="I21" s="17">
-        <v>496</v>
+        <v>548</v>
       </c>
       <c r="J21" s="17">
-        <v>600</v>
+        <v>665</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.333333333333</v>
+        <v>-17.593984962406</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.243937232525</v>
+        <v>-28.366013071895</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.743772241992</v>
+        <v>-10.894308943089</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.422459893048</v>
+        <v>-83.107274969173</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>13</v>
       </c>
       <c r="G22" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H22" s="15">
-        <v>-18.75</v>
+        <v>-35</v>
       </c>
       <c r="I22" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J22" s="14">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K22" s="15">
-        <v>-11.428571428571</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="L22" s="15">
-        <v>-13.888888888888</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="M22" s="15">
-        <v>10.714285714285</v>
+        <v>19.354838709677</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D24" s="14">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="F24" s="14">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="G24" s="14">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.907284768211</v>
+        <v>-20.915032679738</v>
       </c>
       <c r="I24" s="14">
-        <v>660</v>
+        <v>726</v>
       </c>
       <c r="J24" s="14">
-        <v>716</v>
+        <v>792</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.821229050279</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.618369987063</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M24" s="15">
-        <v>-18.316831683168</v>
+        <v>-15.874855156431</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="14">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E25" s="15">
-        <v>-5.263157894736</v>
+        <v>-32.911392405063</v>
       </c>
       <c r="F25" s="14">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="G25" s="14">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.079365079365</v>
+        <v>-28.363636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>558</v>
+        <v>611</v>
       </c>
       <c r="J25" s="14">
-        <v>627</v>
+        <v>706</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.004784688995</v>
+        <v>-13.456090651558</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.285714285714</v>
+        <v>-15.256588072122</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>-35</v>
+        <v>-24</v>
       </c>
       <c r="F26" s="14">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H26" s="15">
-        <v>32.835820895522</v>
+        <v>-2.5</v>
       </c>
       <c r="I26" s="14">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="J26" s="14">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="K26" s="15">
-        <v>11.351351351351</v>
+        <v>5.714285714285</v>
       </c>
       <c r="L26" s="15">
-        <v>10.752688172043</v>
+        <v>2.777777777777</v>
       </c>
       <c r="M26" s="15">
-        <v>83.928571428571</v>
+        <v>76.190476190476</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,13 +1406,13 @@
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-66.666666666666</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="L27" s="15">
-        <v>-42.857142857142</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I28" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J28" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K28" s="15">
-        <v>-10.810810810810</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="L28" s="15">
-        <v>-5.714285714285</v>
+        <v>2.777777777777</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L31" s="15">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -901,26 +901,26 @@
       <c r="E15" s="15">
         <v>-100</v>
       </c>
-      <c r="F15" s="14">
-        <v>2</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-77.777777777777</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M15" s="15">
         <v>300</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>-29.166666666666</v>
+        <v>-64</v>
       </c>
       <c r="I16" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="K16" s="15">
-        <v>-17.1875</v>
+        <v>-26.027397260274</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.1875</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M16" s="15">
-        <v>43.243243243243</v>
+        <v>35</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.117043121149</v>
+        <v>-89.868667917448</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
         <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-58.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.108108108108</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="I17" s="14">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J17" s="14">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.547169811320</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.949152542372</v>
+        <v>-16.535433070866</v>
       </c>
       <c r="M17" s="15">
-        <v>113.04347826087</v>
+        <v>125.531914893617</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.941176470588</v>
+        <v>-29.801324503311</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
+        <v>10</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F18" s="14">
         <v>16</v>
       </c>
-      <c r="E18" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F18" s="14">
-        <v>15</v>
-      </c>
       <c r="G18" s="14">
+        <v>49</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-67.346938775510</v>
+      </c>
+      <c r="I18" s="14">
         <v>52</v>
       </c>
-      <c r="H18" s="15">
-        <v>-71.153846153846</v>
-      </c>
-      <c r="I18" s="14">
-        <v>47</v>
-      </c>
       <c r="J18" s="14">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.465346534653</v>
+        <v>-53.153153153153</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.348837209302</v>
+        <v>-41.573033707865</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.961038961039</v>
+        <v>-38.823529411764</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.754385964912</v>
+        <v>-91.693290734824</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D19" s="14">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E19" s="15">
-        <v>24.137931034482</v>
+        <v>-17.5</v>
       </c>
       <c r="F19" s="14">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G19" s="14">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="H19" s="15">
-        <v>3.149606299212</v>
+        <v>-5.035971223021</v>
       </c>
       <c r="I19" s="14">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="J19" s="14">
-        <v>378</v>
+        <v>418</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.523809523809</v>
+        <v>-10.047846889952</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.301886792452</v>
+        <v>-25.838264299802</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.660714285714</v>
+        <v>-25.544554455445</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.586558044806</v>
+        <v>-82.421692379616</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>-80</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M20" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.468354430379</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E21" s="18">
-        <v>-24.615384615384</v>
+        <v>-32.876712328767</v>
       </c>
       <c r="F21" s="17">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G21" s="17">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.521912350597</v>
+        <v>-26.717557251908</v>
       </c>
       <c r="I21" s="17">
-        <v>548</v>
+        <v>598</v>
       </c>
       <c r="J21" s="17">
-        <v>665</v>
+        <v>738</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.593984962406</v>
+        <v>-18.970189701897</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.366013071895</v>
+        <v>-26.535626535626</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.894308943089</v>
+        <v>-12.700729927007</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.107274969173</v>
+        <v>-83.097795364612</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
         <v>5</v>
       </c>
-      <c r="D22" s="14">
-        <v>10</v>
-      </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F22" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H22" s="15">
-        <v>-35</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I22" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J22" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K22" s="15">
-        <v>-17.777777777777</v>
+        <v>-24</v>
       </c>
       <c r="L22" s="15">
-        <v>-2.631578947368</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="M22" s="15">
-        <v>19.354838709677</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D24" s="14">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.157894736842</v>
+        <v>-27.368421052631</v>
       </c>
       <c r="F24" s="14">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G24" s="14">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.915032679738</v>
+        <v>-23.028391167192</v>
       </c>
       <c r="I24" s="14">
-        <v>726</v>
+        <v>795</v>
       </c>
       <c r="J24" s="14">
-        <v>792</v>
+        <v>887</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.333333333333</v>
+        <v>-10.372040586245</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.285714285714</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="M24" s="15">
-        <v>-15.874855156431</v>
+        <v>-17.1875</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>53</v>
       </c>
       <c r="D25" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E25" s="15">
-        <v>-32.911392405063</v>
+        <v>-36.904761904761</v>
       </c>
       <c r="F25" s="14">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G25" s="14">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.363636363636</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>611</v>
+        <v>666</v>
       </c>
       <c r="J25" s="14">
-        <v>706</v>
+        <v>790</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.456090651558</v>
+        <v>-15.696202531645</v>
       </c>
       <c r="L25" s="15">
-        <v>-15.256588072122</v>
+        <v>-16.331658291457</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E26" s="15">
-        <v>-24</v>
+        <v>-57.575757575757</v>
       </c>
       <c r="F26" s="14">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.5</v>
+        <v>-30.612244897959</v>
       </c>
       <c r="I26" s="14">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="J26" s="14">
-        <v>210</v>
+        <v>243</v>
       </c>
       <c r="K26" s="15">
-        <v>5.714285714285</v>
+        <v>-2.469135802469</v>
       </c>
       <c r="L26" s="15">
-        <v>2.777777777777</v>
+        <v>4.867256637168</v>
       </c>
       <c r="M26" s="15">
-        <v>76.190476190476</v>
+        <v>78.195488721804</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="15">
         <v>-100</v>
       </c>
-      <c r="F27" s="14">
-        <v>2</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-77.777777777777</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>-69.230769230769</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L27" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
         <v>6</v>
       </c>
-      <c r="E28" s="15">
-        <v>-33.333333333333</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G28" s="14">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15">
-        <v>-43.478260869565</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="J28" s="14">
         <v>43</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.953488372093</v>
+        <v>2.325581395348</v>
       </c>
       <c r="L28" s="15">
-        <v>2.777777777777</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-88.888888888888</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>-64</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J16" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K16" s="15">
-        <v>-26.027397260274</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.739130434782</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="M16" s="15">
-        <v>35</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.868667917448</v>
+        <v>-89.932885906040</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.829268292682</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="I17" s="14">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="J17" s="14">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.169491525423</v>
+        <v>-8.396946564885</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.535433070866</v>
+        <v>-12.408759124087</v>
       </c>
       <c r="M17" s="15">
-        <v>125.531914893617</v>
+        <v>140</v>
       </c>
       <c r="N17" s="15">
-        <v>-29.801324503311</v>
+        <v>-25.465838509316</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>5</v>
       </c>
-      <c r="D18" s="14">
-        <v>10</v>
-      </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H18" s="15">
-        <v>-67.346938775510</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J18" s="14">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.153153153153</v>
+        <v>-54.310344827586</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.573033707865</v>
+        <v>-44.791666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-38.823529411764</v>
+        <v>-39.772727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.693290734824</v>
+        <v>-92.251461988304</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,72 +1057,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="14">
         <v>40</v>
       </c>
       <c r="E19" s="15">
-        <v>-17.5</v>
+        <v>-22.5</v>
       </c>
       <c r="F19" s="14">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G19" s="14">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.035971223021</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="I19" s="14">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="J19" s="14">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.047846889952</v>
+        <v>-11.572052401746</v>
       </c>
       <c r="L19" s="15">
-        <v>-25.838264299802</v>
+        <v>-24.440298507462</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.544554455445</v>
+        <v>-25.138632162661</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.421692379616</v>
+        <v>-82.684908080376</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="15">
         <v>-63.636363636363</v>
@@ -1131,7 +1131,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-95</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E21" s="18">
-        <v>-32.876712328767</v>
+        <v>-21.875</v>
       </c>
       <c r="F21" s="17">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G21" s="17">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.717557251908</v>
+        <v>-23.166023166023</v>
       </c>
       <c r="I21" s="17">
-        <v>598</v>
+        <v>648</v>
       </c>
       <c r="J21" s="17">
-        <v>738</v>
+        <v>802</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.970189701897</v>
+        <v>-19.201995012468</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.535626535626</v>
+        <v>-25.345622119815</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.700729927007</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.097795364612</v>
+        <v>-83.303272352486</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" s="15">
-        <v>-80</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G22" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H22" s="15">
-        <v>-63.636363636363</v>
+        <v>-44</v>
       </c>
       <c r="I22" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J22" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K22" s="15">
-        <v>-24</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L22" s="15">
-        <v>-7.317073170731</v>
+        <v>2.272727272727</v>
       </c>
       <c r="M22" s="15">
-        <v>5.555555555555</v>
+        <v>18.421052631578</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D24" s="14">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.368421052631</v>
+        <v>-23.655913978494</v>
       </c>
       <c r="F24" s="14">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="G24" s="14">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.028391167192</v>
+        <v>-20.238095238095</v>
       </c>
       <c r="I24" s="14">
-        <v>795</v>
+        <v>867</v>
       </c>
       <c r="J24" s="14">
-        <v>887</v>
+        <v>980</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.372040586245</v>
+        <v>-11.530612244898</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.516129032258</v>
+        <v>-14.833005893909</v>
       </c>
       <c r="M24" s="15">
-        <v>-17.1875</v>
+        <v>-18.130311614730</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D25" s="14">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.904761904761</v>
+        <v>-29.885057471264</v>
       </c>
       <c r="F25" s="14">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="G25" s="14">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.035830618892</v>
       </c>
       <c r="I25" s="14">
-        <v>666</v>
+        <v>728</v>
       </c>
       <c r="J25" s="14">
-        <v>790</v>
+        <v>877</v>
       </c>
       <c r="K25" s="15">
-        <v>-15.696202531645</v>
+        <v>-16.989737742303</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.331658291457</v>
+        <v>-16.894977168949</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-57.575757575757</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
         <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H26" s="15">
-        <v>-30.612244897959</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="J26" s="14">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.469135802469</v>
+        <v>-0.766283524904</v>
       </c>
       <c r="L26" s="15">
-        <v>4.867256637168</v>
+        <v>7.468879668049</v>
       </c>
       <c r="M26" s="15">
-        <v>78.195488721804</v>
+        <v>72.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>4</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-75</v>
       </c>
       <c r="F28" s="14">
         <v>17</v>
       </c>
       <c r="G28" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" s="15">
-        <v>13.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I28" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J28" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K28" s="15">
-        <v>2.325581395348</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="L28" s="15">
-        <v>15.789473684210</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L31" s="15">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -914,19 +914,19 @@
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-69.230769230769</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L15" s="15">
-        <v>-55.555555555555</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M15" s="15">
         <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="I16" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J16" s="14">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.076923076923</v>
+        <v>-22.619047619047</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.077922077922</v>
+        <v>-25.287356321839</v>
       </c>
       <c r="M16" s="15">
-        <v>33.333333333333</v>
+        <v>41.304347826087</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.932885906040</v>
+        <v>-89.827856025039</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>7.692307692307</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.555555555555</v>
+        <v>-35.087719298245</v>
       </c>
       <c r="I17" s="14">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="J17" s="14">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.396946564885</v>
+        <v>-14.569536423841</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.408759124087</v>
+        <v>-13.422818791946</v>
       </c>
       <c r="M17" s="15">
-        <v>140</v>
+        <v>122.413793103448</v>
       </c>
       <c r="N17" s="15">
-        <v>-25.465838509316</v>
+        <v>-27.528089887640</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-62.790697674418</v>
       </c>
       <c r="I18" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J18" s="14">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="K18" s="15">
-        <v>-54.310344827586</v>
+        <v>-53.90625</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.791666666666</v>
+        <v>-44.339622641509</v>
       </c>
       <c r="M18" s="15">
-        <v>-39.772727272727</v>
+        <v>-36.559139784946</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.251461988304</v>
+        <v>-92.164674634794</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D19" s="14">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G19" s="14">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.255319148936</v>
+        <v>-6.993006993006</v>
       </c>
       <c r="I19" s="14">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="J19" s="14">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.572052401746</v>
+        <v>-10.772357723577</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.440298507462</v>
+        <v>-22.711267605633</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.138632162661</v>
+        <v>-24.179620034542</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.684908080376</v>
+        <v>-82.558601509733</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
         <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.652173913043</v>
+        <v>-95.192307692307</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D21" s="17">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.875</v>
+        <v>-23.287671232876</v>
       </c>
       <c r="F21" s="17">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G21" s="17">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.166023166023</v>
+        <v>-25.818181818181</v>
       </c>
       <c r="I21" s="17">
-        <v>648</v>
+        <v>703</v>
       </c>
       <c r="J21" s="17">
-        <v>802</v>
+        <v>875</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.201995012468</v>
+        <v>-19.657142857142</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.345622119815</v>
+        <v>-24.812834224598</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.475409836065</v>
+        <v>-10.331632653061</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.303272352486</v>
+        <v>-83.26588907403</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>5</v>
       </c>
       <c r="D22" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="F22" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G22" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H22" s="15">
-        <v>-44</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I22" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J22" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K22" s="15">
-        <v>-21.052631578947</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="L22" s="15">
-        <v>2.272727272727</v>
+        <v>2.040816326530</v>
       </c>
       <c r="M22" s="15">
-        <v>18.421052631578</v>
+        <v>28.205128205128</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D24" s="14">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.655913978494</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="F24" s="14">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G24" s="14">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.238095238095</v>
+        <v>-20.294117647058</v>
       </c>
       <c r="I24" s="14">
-        <v>867</v>
+        <v>930</v>
       </c>
       <c r="J24" s="14">
-        <v>980</v>
+        <v>1056</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.530612244898</v>
+        <v>-11.931818181818</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.833005893909</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M24" s="15">
-        <v>-18.130311614730</v>
+        <v>-19.480519480519</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D25" s="14">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E25" s="15">
-        <v>-29.885057471264</v>
+        <v>-28.358208955223</v>
       </c>
       <c r="F25" s="14">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G25" s="14">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.035830618892</v>
+        <v>-31.230283911671</v>
       </c>
       <c r="I25" s="14">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="J25" s="14">
-        <v>877</v>
+        <v>944</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.989737742303</v>
+        <v>-17.796610169491</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.894977168949</v>
+        <v>-17.883597883597</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G26" s="14">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H26" s="15">
-        <v>-29.166666666666</v>
+        <v>-26.804123711340</v>
       </c>
       <c r="I26" s="14">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="J26" s="14">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.766283524904</v>
+        <v>-2.482269503546</v>
       </c>
       <c r="L26" s="15">
-        <v>7.468879668049</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>72.666666666666</v>
+        <v>68.711656441717</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1406,13 +1406,13 @@
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
+        <v>-73.333333333333</v>
+      </c>
+      <c r="L27" s="15">
         <v>-71.428571428571</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-63.636363636363</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" s="15">
-        <v>21.428571428571</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I28" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J28" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.255319148936</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="15">
-        <v>-2.173913043478</v>
+        <v>-5.769230769230</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
         <v>-80</v>
@@ -1538,7 +1538,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
         <v>-75</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="L31" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-71.428571428571</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-16.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F16" s="14">
         <v>14</v>
@@ -952,22 +952,22 @@
         <v>-48.148148148148</v>
       </c>
       <c r="I16" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J16" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K16" s="15">
-        <v>-22.619047619047</v>
+        <v>-25.274725274725</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.287356321839</v>
+        <v>-26.881720430107</v>
       </c>
       <c r="M16" s="15">
-        <v>41.304347826087</v>
+        <v>38.775510204081</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.827856025039</v>
+        <v>-90.144927536231</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G17" s="14">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.087719298245</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J17" s="14">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.569536423841</v>
+        <v>-11.038961038961</v>
       </c>
       <c r="L17" s="15">
-        <v>-13.422818791946</v>
+        <v>-12.179487179487</v>
       </c>
       <c r="M17" s="15">
-        <v>122.413793103448</v>
+        <v>132.203389830508</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.528089887640</v>
+        <v>-26.737967914438</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G18" s="14">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H18" s="15">
-        <v>-62.790697674418</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="I18" s="14">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="J18" s="14">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.90625</v>
+        <v>-50.359712230215</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.339622641509</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="M18" s="15">
-        <v>-36.559139784946</v>
+        <v>-29.591836734693</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.164674634794</v>
+        <v>-91.276864728192</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D19" s="14">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>81.818181818181</v>
       </c>
       <c r="F19" s="14">
         <v>133</v>
       </c>
       <c r="G19" s="14">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.993006993006</v>
+        <v>-2.205882352941</v>
       </c>
       <c r="I19" s="14">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="J19" s="14">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.772357723577</v>
+        <v>-7.198443579766</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.711267605633</v>
+        <v>-20.895522388059</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.179620034542</v>
+        <v>-23.188405797101</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.558601509733</v>
+        <v>-82.411504424778</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
         <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-58.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M20" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.192307692307</v>
+        <v>-94.545454545454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D21" s="17">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.287671232876</v>
+        <v>39.534883720930</v>
       </c>
       <c r="F21" s="17">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G21" s="17">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.818181818181</v>
+        <v>-15.415019762845</v>
       </c>
       <c r="I21" s="17">
-        <v>703</v>
+        <v>764</v>
       </c>
       <c r="J21" s="17">
-        <v>875</v>
+        <v>918</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.657142857142</v>
+        <v>-16.775599128540</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.812834224598</v>
+        <v>-22.515212981744</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.331632653061</v>
+        <v>-8.502994011976</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.26588907403</v>
+        <v>-83.022222222222</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" s="14">
         <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F22" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H22" s="15">
-        <v>-30.769230769230</v>
+        <v>-5</v>
       </c>
       <c r="I22" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J22" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K22" s="15">
-        <v>-18.032786885245</v>
+        <v>-12.307692307692</v>
       </c>
       <c r="L22" s="15">
-        <v>2.040816326530</v>
+        <v>5.555555555555</v>
       </c>
       <c r="M22" s="15">
-        <v>28.205128205128</v>
+        <v>42.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="14">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.421052631578</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="F24" s="14">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="G24" s="14">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.294117647058</v>
+        <v>-19.879518072289</v>
       </c>
       <c r="I24" s="14">
-        <v>930</v>
+        <v>992</v>
       </c>
       <c r="J24" s="14">
-        <v>1056</v>
+        <v>1124</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.931818181818</v>
+        <v>-11.743772241992</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.963573287077</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.480519480519</v>
+        <v>-21.704814522494</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D25" s="14">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E25" s="15">
-        <v>-28.358208955223</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="F25" s="14">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G25" s="14">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.230283911671</v>
+        <v>-28.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>776</v>
+        <v>828</v>
       </c>
       <c r="J25" s="14">
-        <v>944</v>
+        <v>1006</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.796610169491</v>
+        <v>-17.693836978131</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.883597883597</v>
+        <v>-17.775571002979</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>13</v>
+      </c>
+      <c r="D26" s="14">
         <v>15</v>
       </c>
-      <c r="D26" s="14">
-        <v>21</v>
-      </c>
       <c r="E26" s="15">
-        <v>-28.571428571428</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G26" s="14">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="H26" s="15">
-        <v>-26.804123711340</v>
+        <v>-26.436781609195</v>
       </c>
       <c r="I26" s="14">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="J26" s="14">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.482269503546</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="L26" s="15">
-        <v>4.166666666666</v>
+        <v>2.857142857142</v>
       </c>
       <c r="M26" s="15">
-        <v>68.711656441717</v>
+        <v>54.010695187165</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-73.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-71.428571428571</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>23.076923076923</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J28" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K28" s="15">
-        <v>-2</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="L28" s="15">
-        <v>-5.769230769230</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>25</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>200</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>-64.285714285714</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>-54.545454545454</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-71.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="15">
-        <v>-48.148148148148</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I16" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J16" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.274725274725</v>
+        <v>-28.282828282828</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.881720430107</v>
+        <v>-33.644859813084</v>
       </c>
       <c r="M16" s="15">
-        <v>38.775510204081</v>
+        <v>42</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.144927536231</v>
+        <v>-90.287277701778</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>166.666666666667</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F17" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G17" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="I17" s="14">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="J17" s="14">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.038961038961</v>
+        <v>-11.695906432748</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.179487179487</v>
+        <v>-9.036144578313</v>
       </c>
       <c r="M17" s="15">
-        <v>132.203389830508</v>
+        <v>143.548387096774</v>
       </c>
       <c r="N17" s="15">
-        <v>-26.737967914438</v>
+        <v>-27.403846153846</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.105263157894</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I18" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J18" s="14">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K18" s="15">
-        <v>-50.359712230215</v>
+        <v>-49.655172413793</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.111111111111</v>
+        <v>-37.606837606837</v>
       </c>
       <c r="M18" s="15">
-        <v>-29.591836734693</v>
+        <v>-27.722772277227</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.276864728192</v>
+        <v>-91.183574879227</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E19" s="15">
-        <v>81.818181818181</v>
+        <v>-12</v>
       </c>
       <c r="F19" s="14">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="G19" s="14">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.205882352941</v>
+        <v>1.652892561983</v>
       </c>
       <c r="I19" s="14">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="J19" s="14">
-        <v>514</v>
+        <v>539</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.198443579766</v>
+        <v>-7.792207792207</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.895522388059</v>
+        <v>-21.978021978022</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.188405797101</v>
+        <v>-25.150602409638</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.411504424778</v>
+        <v>-83.002735978112</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-50</v>
+      </c>
+      <c r="M20" s="15">
         <v>0</v>
       </c>
-      <c r="L20" s="15">
-        <v>-53.846153846153</v>
-      </c>
-      <c r="M20" s="15">
-        <v>-14.285714285714</v>
-      </c>
       <c r="N20" s="15">
-        <v>-94.545454545454</v>
+        <v>-93.859649122807</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E21" s="18">
-        <v>39.534883720930</v>
+        <v>-20.338983050847</v>
       </c>
       <c r="F21" s="17">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G21" s="17">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.415019762845</v>
+        <v>-11.715481171548</v>
       </c>
       <c r="I21" s="17">
-        <v>764</v>
+        <v>809</v>
       </c>
       <c r="J21" s="17">
-        <v>918</v>
+        <v>977</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.775599128540</v>
+        <v>-17.195496417604</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.515212981744</v>
+        <v>-23.317535545023</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.502994011976</v>
+        <v>-8.587570621468</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.022222222222</v>
+        <v>-83.201827242524</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>7</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>75</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
+        <v>17</v>
+      </c>
+      <c r="G22" s="14">
         <v>19</v>
       </c>
-      <c r="G22" s="14">
-        <v>20</v>
-      </c>
       <c r="H22" s="15">
-        <v>-5</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I22" s="14">
         <v>57</v>
       </c>
       <c r="J22" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K22" s="15">
-        <v>-12.307692307692</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L22" s="15">
-        <v>5.555555555555</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>42.5</v>
+        <v>32.558139534883</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D24" s="14">
         <v>68</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.294117647058</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G24" s="14">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.879518072289</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="I24" s="14">
-        <v>992</v>
+        <v>1060</v>
       </c>
       <c r="J24" s="14">
-        <v>1124</v>
+        <v>1192</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.743772241992</v>
+        <v>-11.073825503355</v>
       </c>
       <c r="L24" s="15">
-        <v>-13.963573287077</v>
+        <v>-14.100486223662</v>
       </c>
       <c r="M24" s="15">
-        <v>-21.704814522494</v>
+        <v>-22.627737226277</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D25" s="14">
         <v>62</v>
       </c>
       <c r="E25" s="15">
-        <v>-14.516129032258</v>
+        <v>-24.193548387096</v>
       </c>
       <c r="F25" s="14">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G25" s="14">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="H25" s="15">
-        <v>-28.333333333333</v>
+        <v>-24.820143884892</v>
       </c>
       <c r="I25" s="14">
-        <v>828</v>
+        <v>875</v>
       </c>
       <c r="J25" s="14">
-        <v>1006</v>
+        <v>1068</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.693836978131</v>
+        <v>-18.071161048689</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.775571002979</v>
+        <v>-19.280442804428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G26" s="14">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>-26.436781609195</v>
+        <v>-5.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="J26" s="14">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.030303030303</v>
+        <v>-2.830188679245</v>
       </c>
       <c r="L26" s="15">
-        <v>2.857142857142</v>
+        <v>3.691275167785</v>
       </c>
       <c r="M26" s="15">
-        <v>54.010695187165</v>
+        <v>55.276381909547</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>4</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>300</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>-66.666666666666</v>
+        <v>-43.75</v>
       </c>
       <c r="L27" s="15">
-        <v>-64.285714285714</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>12</v>
       </c>
-      <c r="G28" s="14">
-        <v>10</v>
-      </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J28" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.660377358490</v>
+        <v>-3.636363636363</v>
       </c>
       <c r="L28" s="15">
-        <v>-15.254237288135</v>
+        <v>-17.1875</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L31" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
-        <v>-46.666666666666</v>
+        <v>-43.75</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M15" s="15">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-62.5</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>-42.307692307692</v>
+        <v>-59.259259259259</v>
       </c>
       <c r="I16" s="14">
         <v>71</v>
       </c>
       <c r="J16" s="14">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K16" s="15">
-        <v>-28.282828282828</v>
+        <v>-32.380952380952</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.644859813084</v>
+        <v>-37.719298245614</v>
       </c>
       <c r="M16" s="15">
-        <v>42</v>
+        <v>39.215686274509</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.287277701778</v>
+        <v>-90.718954248366</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
         <v>14</v>
       </c>
-      <c r="D17" s="14">
-        <v>17</v>
-      </c>
       <c r="E17" s="15">
-        <v>-17.647058823529</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.207547169811</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="J17" s="14">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.695906432748</v>
+        <v>-11.891891891891</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.036144578313</v>
+        <v>-5.780346820809</v>
       </c>
       <c r="M17" s="15">
-        <v>143.548387096774</v>
+        <v>154.6875</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.403846153846</v>
+        <v>-27.876106194690</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H18" s="15">
-        <v>-41.176470588235</v>
+        <v>-34.375</v>
       </c>
       <c r="I18" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J18" s="14">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.655172413793</v>
+        <v>-49.324324324324</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.606837606837</v>
+        <v>-41.40625</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.722772277227</v>
+        <v>-29.245283018867</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.183574879227</v>
+        <v>-91.228070175438</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" s="15">
-        <v>-12</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G19" s="14">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="H19" s="15">
-        <v>1.652892561983</v>
+        <v>11.009174311926</v>
       </c>
       <c r="I19" s="14">
-        <v>497</v>
+        <v>526</v>
       </c>
       <c r="J19" s="14">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.792207792207</v>
+        <v>-7.231040564373</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.978021978022</v>
+        <v>-22.189349112426</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.150602409638</v>
+        <v>-26.433566433566</v>
       </c>
       <c r="N19" s="15">
-        <v>-83.002735978112</v>
+        <v>-82.988357050452</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="15">
-        <v>-50</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
         <v>8</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.859649122807</v>
+        <v>-92.682926829268</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.338983050847</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="F21" s="17">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G21" s="17">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.715481171548</v>
+        <v>-9.691629955947</v>
       </c>
       <c r="I21" s="17">
-        <v>809</v>
+        <v>855</v>
       </c>
       <c r="J21" s="17">
-        <v>977</v>
+        <v>1029</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.195496417604</v>
+        <v>-16.909620991253</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.317535545023</v>
+        <v>-23.660714285714</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.587570621468</v>
+        <v>-9.427966101694</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.201827242524</v>
+        <v>-83.142744479495</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H22" s="15">
-        <v>-10.526315789473</v>
+        <v>-12.5</v>
       </c>
       <c r="I22" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J22" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K22" s="15">
-        <v>-17.391304347826</v>
+        <v>-19.178082191780</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>32.558139534883</v>
+        <v>25.531914893617</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D24" s="14">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-10.126582278481</v>
       </c>
       <c r="F24" s="14">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G24" s="14">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.114754098360</v>
+        <v>-9.278350515463</v>
       </c>
       <c r="I24" s="14">
-        <v>1060</v>
+        <v>1131</v>
       </c>
       <c r="J24" s="14">
-        <v>1192</v>
+        <v>1271</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.073825503355</v>
+        <v>-11.014948859166</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.100486223662</v>
+        <v>-14.898419864559</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.627737226277</v>
+        <v>-22.321428571428</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D25" s="14">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E25" s="15">
-        <v>-24.193548387096</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F25" s="14">
         <v>209</v>
       </c>
       <c r="G25" s="14">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="H25" s="15">
-        <v>-24.820143884892</v>
+        <v>-13.991769547325</v>
       </c>
       <c r="I25" s="14">
-        <v>875</v>
+        <v>936</v>
       </c>
       <c r="J25" s="14">
-        <v>1068</v>
+        <v>1120</v>
       </c>
       <c r="K25" s="15">
-        <v>-18.071161048689</v>
+        <v>-16.428571428571</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.280442804428</v>
+        <v>-20.340425531914</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F26" s="14">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.333333333333</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="I26" s="14">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="J26" s="14">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.830188679245</v>
+        <v>-2.388059701492</v>
       </c>
       <c r="L26" s="15">
-        <v>3.691275167785</v>
+        <v>3.481012658227</v>
       </c>
       <c r="M26" s="15">
-        <v>55.276381909547</v>
+        <v>58.737864077669</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-43.75</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J28" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.636363636363</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="L28" s="15">
-        <v>-17.1875</v>
+        <v>-13.235294117647</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>-14.285714285714</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,30 +885,30 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -923,10 +923,10 @@
         <v>-25</v>
       </c>
       <c r="M15" s="15">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="N15" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-83.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H16" s="15">
-        <v>-59.259259259259</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J16" s="14">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K16" s="15">
-        <v>-32.380952380952</v>
+        <v>-33.035714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.719298245614</v>
+        <v>-39.516129032258</v>
       </c>
       <c r="M16" s="15">
-        <v>39.215686274509</v>
+        <v>44.230769230769</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.718954248366</v>
+        <v>-90.853658536585</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
         <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F17" s="14">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.222222222222</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J17" s="14">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.891891891891</v>
+        <v>-17.085427135678</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.780346820809</v>
+        <v>-12.234042553191</v>
       </c>
       <c r="M17" s="15">
-        <v>154.6875</v>
+        <v>142.647058823529</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.876106194690</v>
+        <v>-31.818181818181</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H18" s="15">
-        <v>-34.375</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J18" s="14">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.324324324324</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.40625</v>
+        <v>-42.753623188405</v>
       </c>
       <c r="M18" s="15">
-        <v>-29.245283018867</v>
+        <v>-27.522935779816</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.228070175438</v>
+        <v>-91.093573844419</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D19" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>7.142857142857</v>
+        <v>81.818181818181</v>
       </c>
       <c r="F19" s="14">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G19" s="14">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H19" s="15">
-        <v>11.009174311926</v>
+        <v>36.082474226804</v>
       </c>
       <c r="I19" s="14">
-        <v>526</v>
+        <v>567</v>
       </c>
       <c r="J19" s="14">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.231040564373</v>
+        <v>-3.735144312393</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.189349112426</v>
+        <v>-19.801980198019</v>
       </c>
       <c r="M19" s="15">
-        <v>-26.433566433566</v>
+        <v>-24.900662251655</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.988357050452</v>
+        <v>-82.478368355995</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,13 +1107,13 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
         <v>9</v>
@@ -1125,13 +1125,13 @@
         <v>12.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M20" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.682926829268</v>
+        <v>-93.181818181818</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.615384615384</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="F21" s="17">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G21" s="17">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.691629955947</v>
+        <v>-2.415458937198</v>
       </c>
       <c r="I21" s="17">
-        <v>855</v>
+        <v>906</v>
       </c>
       <c r="J21" s="17">
-        <v>1029</v>
+        <v>1082</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.909620991253</v>
+        <v>-16.266173752310</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.660714285714</v>
+        <v>-23.737373737373</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.427966101694</v>
+        <v>-8.853118712273</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.142744479495</v>
+        <v>-83.005064715813</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
+        <v>12</v>
+      </c>
+      <c r="G22" s="14">
         <v>14</v>
       </c>
-      <c r="G22" s="14">
-        <v>16</v>
-      </c>
       <c r="H22" s="15">
-        <v>-12.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I22" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J22" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K22" s="15">
-        <v>-19.178082191780</v>
+        <v>-17.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-4.615384615384</v>
       </c>
       <c r="M22" s="15">
-        <v>25.531914893617</v>
+        <v>29.166666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D24" s="14">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.126582278481</v>
+        <v>-23.595505617977</v>
       </c>
       <c r="F24" s="14">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G24" s="14">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.278350515463</v>
+        <v>-11.842105263157</v>
       </c>
       <c r="I24" s="14">
-        <v>1131</v>
+        <v>1199</v>
       </c>
       <c r="J24" s="14">
-        <v>1271</v>
+        <v>1360</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.014948859166</v>
+        <v>-11.838235294117</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.898419864559</v>
+        <v>-15.265017667844</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.321428571428</v>
+        <v>-22.744845360824</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D25" s="14">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E25" s="15">
-        <v>15.384615384615</v>
+        <v>-7.246376811594</v>
       </c>
       <c r="F25" s="14">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="G25" s="14">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H25" s="15">
-        <v>-13.991769547325</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>936</v>
+        <v>999</v>
       </c>
       <c r="J25" s="14">
-        <v>1120</v>
+        <v>1189</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.428571428571</v>
+        <v>-15.979814970563</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.340425531914</v>
+        <v>-19.823434991974</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>11.764705882352</v>
+        <v>-52</v>
       </c>
       <c r="F26" s="14">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G26" s="14">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.108108108108</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="J26" s="14">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.388059701492</v>
+        <v>-6.111111111111</v>
       </c>
       <c r="L26" s="15">
-        <v>3.481012658227</v>
+        <v>0.895522388059</v>
       </c>
       <c r="M26" s="15">
-        <v>58.737864077669</v>
+        <v>57.943925233644</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1412,7 +1412,7 @@
         <v>-41.176470588235</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F28" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G28" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="I28" s="14">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J28" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.278688524590</v>
+        <v>-4.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>-13.235294117647</v>
+        <v>-4.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-014pct.xlsx
+++ b/data/source/weekly/cs-en-us-014pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K15" s="15">
-        <v>-43.75</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
         <v>-25</v>
@@ -943,31 +943,31 @@
         <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
         <v>28</v>
       </c>
       <c r="H16" s="15">
-        <v>-67.857142857142</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J16" s="14">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.035714285714</v>
+        <v>-34.453781512605</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.516129032258</v>
+        <v>-41.353383458646</v>
       </c>
       <c r="M16" s="15">
-        <v>44.230769230769</v>
+        <v>47.169811320754</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.853658536585</v>
+        <v>-91.106043329532</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
         <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-85.714285714285</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="H17" s="15">
-        <v>-29.166666666666</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="I17" s="14">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="J17" s="14">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.085427135678</v>
+        <v>-16.431924882629</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.234042553191</v>
+        <v>-8.717948717948</v>
       </c>
       <c r="M17" s="15">
-        <v>142.647058823529</v>
+        <v>150.704225352113</v>
       </c>
       <c r="N17" s="15">
-        <v>-31.818181818181</v>
+        <v>-29.921259842519</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J18" s="14">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-46.987951807228</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.753623188405</v>
+        <v>-39.726027397260</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.522935779816</v>
+        <v>-25.423728813559</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.093573844419</v>
+        <v>-90.677966101694</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>29</v>
+      </c>
+      <c r="D19" s="14">
         <v>40</v>
       </c>
-      <c r="D19" s="14">
-        <v>22</v>
-      </c>
       <c r="E19" s="15">
-        <v>81.818181818181</v>
+        <v>-27.5</v>
       </c>
       <c r="F19" s="14">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G19" s="14">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="H19" s="15">
-        <v>36.082474226804</v>
+        <v>5.217391304347</v>
       </c>
       <c r="I19" s="14">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="J19" s="14">
-        <v>589</v>
+        <v>629</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.735144312393</v>
+        <v>-5.087440381558</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.801980198019</v>
+        <v>-20.187165775401</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.900662251655</v>
+        <v>-25.838509316770</v>
       </c>
       <c r="N19" s="15">
-        <v>-82.478368355995</v>
+        <v>-82.569343065693</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-47.058823529411</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M20" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.181818181818</v>
+        <v>-93.661971830985</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.660377358490</v>
+        <v>-31.944444444444</v>
       </c>
       <c r="F21" s="17">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="G21" s="17">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.415458937198</v>
+        <v>-18.220338983050</v>
       </c>
       <c r="I21" s="17">
-        <v>906</v>
+        <v>962</v>
       </c>
       <c r="J21" s="17">
-        <v>1082</v>
+        <v>1154</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.266173752310</v>
+        <v>-16.637781629116</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.737373737373</v>
+        <v>-23.346613545816</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.853118712273</v>
+        <v>-9.073724007561</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.005064715813</v>
+        <v>-82.991513437058</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
         <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G22" s="14">
         <v>14</v>
       </c>
       <c r="H22" s="15">
-        <v>-14.285714285714</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I22" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J22" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K22" s="15">
-        <v>-17.333333333333</v>
+        <v>-16.455696202531</v>
       </c>
       <c r="L22" s="15">
-        <v>-4.615384615384</v>
+        <v>-1.492537313432</v>
       </c>
       <c r="M22" s="15">
-        <v>29.166666666666</v>
+        <v>37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>52</v>
+      </c>
+      <c r="D24" s="14">
         <v>68</v>
       </c>
-      <c r="D24" s="14">
-        <v>89</v>
-      </c>
       <c r="E24" s="15">
-        <v>-23.595505617977</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F24" s="14">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="G24" s="14">
         <v>304</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.842105263157</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I24" s="14">
-        <v>1199</v>
+        <v>1245</v>
       </c>
       <c r="J24" s="14">
-        <v>1360</v>
+        <v>1428</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.838235294117</v>
+        <v>-12.815126050420</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.265017667844</v>
+        <v>-16.274377942165</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.744845360824</v>
+        <v>-23.759951010410</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D25" s="14">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E25" s="15">
-        <v>-7.246376811594</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G25" s="14">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.571428571428</v>
+        <v>-13.414634146341</v>
       </c>
       <c r="I25" s="14">
-        <v>999</v>
+        <v>1037</v>
       </c>
       <c r="J25" s="14">
-        <v>1189</v>
+        <v>1252</v>
       </c>
       <c r="K25" s="15">
-        <v>-15.979814970563</v>
+        <v>-17.172523961661</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.823434991974</v>
+        <v>-20.657995409334</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>-52</v>
+        <v>30</v>
       </c>
       <c r="F26" s="14">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.666666666666</v>
+        <v>-6.024096385542</v>
       </c>
       <c r="I26" s="14">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="J26" s="14">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.111111111111</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="L26" s="15">
-        <v>0.895522388059</v>
+        <v>3.107344632768</v>
       </c>
       <c r="M26" s="15">
-        <v>57.943925233644</v>
+        <v>64.414414414414</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K27" s="15">
-        <v>-41.176470588235</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="L27" s="15">
         <v>-37.5</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>-11.111111111111</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F28" s="14">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G28" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H28" s="15">
-        <v>-10</v>
+        <v>12.5</v>
       </c>
       <c r="I28" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J28" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K28" s="15">
-        <v>-4.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.285714285714</v>
+        <v>4.054054054054</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="D31" s="14">
         <v>1</v>
       </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
